--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_133_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_133_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7428</v>
+        <v>4.5412</v>
       </c>
       <c r="E2" t="n">
         <v>0.8424</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9004</v>
+        <v>3.6988</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0063</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0738</v>
+        <v>-0.1278</v>
       </c>
       <c r="T2" t="n">
         <v>-0.7073</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7811</v>
+        <v>0.5794</v>
       </c>
       <c r="V2" t="n">
         <v>1.8919</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>T. ENNIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.217</v>
+        <v>3.0695</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3493</v>
+        <v>2.1318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8676</v>
+        <v>0.9378</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5318</v>
+        <v>1.9118</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9529</v>
+        <v>0.1284</v>
       </c>
       <c r="I3" t="n">
-        <v>0.579</v>
+        <v>1.7833</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5072</v>
+        <v>2.3872</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3968</v>
+        <v>0.3396</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>2.0476</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0246</v>
+        <v>-0.4755</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4439</v>
+        <v>-0.2112</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4685</v>
+        <v>-0.2643</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.381</v>
+        <v>0.23</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0895</v>
+        <v>-0.2555</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2915</v>
+        <v>0.4854</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. ENNIS</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6603</v>
+        <v>2.3818</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7898</v>
+        <v>-0.8207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8706</v>
+        <v>3.2025</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9118</v>
+        <v>1.1926</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1284</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7833</v>
+        <v>0.6558</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3872</v>
+        <v>1.3609</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3396</v>
+        <v>0.5412</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0476</v>
+        <v>0.8196</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4755</v>
+        <v>-0.1682</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2112</v>
+        <v>-0.0044</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2643</v>
+        <v>-0.1638</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1792</v>
+        <v>-0.2025</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5975</v>
+        <v>-1.0218</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4182</v>
+        <v>0.8193</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.559</v>
+        <v>2.0763</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4419</v>
+        <v>1.2759</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0009</v>
+        <v>0.8004</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1926</v>
+        <v>2.5318</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5368000000000001</v>
+        <v>1.9529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6558</v>
+        <v>0.579</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3609</v>
+        <v>2.5072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5412</v>
+        <v>2.3968</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8196</v>
+        <v>0.1104</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1682</v>
+        <v>0.0246</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0044</v>
+        <v>-0.4439</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1638</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0253</v>
+        <v>1.2404</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.643</v>
+        <v>0.016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6177</v>
+        <v>1.2243</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3257</v>
+        <v>1.5998</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0827</v>
+        <v>0.0234</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4083</v>
+        <v>1.5764</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6499</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.344</v>
+        <v>-0.0698</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4086</v>
+        <v>-0.3025</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0646</v>
+        <v>0.2326</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2156</v>
+        <v>0.3483</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4313</v>
+        <v>-2.2073</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6469</v>
+        <v>2.5556</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0131</v>
+        <v>-1.8355</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6961</v>
+        <v>-0.2797</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.683</v>
+        <v>-1.5559</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1748</v>
+        <v>-1.546</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9612</v>
+        <v>-0.0469</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7863</v>
+        <v>-1.4991</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1617</v>
+        <v>-0.2895</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2651</v>
+        <v>-0.2327</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8966</v>
+        <v>-0.0568</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7622</v>
+        <v>-0.0481</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3339</v>
+        <v>-0.5737</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4283</v>
+        <v>0.5256</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3587</v>
+        <v>-0.276</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6791</v>
+        <v>2.27</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3204</v>
+        <v>-2.546</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8355</v>
+        <v>1.0131</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2797</v>
+        <v>2.6961</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5559</v>
+        <v>-1.683</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.546</v>
+        <v>2.1748</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0469</v>
+        <v>2.9612</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4991</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2895</v>
+        <v>-1.1617</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2327</v>
+        <v>-0.2651</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0568</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7552</v>
+        <v>-0.8226</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0455</v>
+        <v>-0.4951</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2904</v>
+        <v>-0.3275</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.499</v>
+        <v>-0.3139</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8943</v>
+        <v>1.0123</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3933</v>
+        <v>-1.3261</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0106</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4859</v>
+        <v>-0.3007</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9304</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5735</v>
+        <v>-2.6855</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.883</v>
+        <v>-5.659</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3095</v>
+        <v>2.9734</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1042</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2265</v>
+        <v>1.1145</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7073</v>
+        <v>-0.4832</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9338</v>
+        <v>1.5977</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4678</v>
+        <v>-3.2313</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4691</v>
+        <v>-3.9973</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0012</v>
+        <v>0.766</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8956</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8764</v>
+        <v>-0.6398</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3443</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4679</v>
+        <v>0.2326</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.390199999999997</v>
+        <v>7.510199999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2487</v>
+        <v>-5.128499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>12.6387</v>
+        <v>12.6388</v>
       </c>
       <c r="G12" t="n">
         <v>0.1472000000000002</v>
@@ -1366,7 +1366,7 @@
         <v>4.4197</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4411</v>
+        <v>5.441099999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-1.0213</v>
@@ -1390,19 +1390,19 @@
         <v>18.5562</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7469000000000002</v>
+        <v>0.3736</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.071300000000001</v>
+        <v>-4.9511</v>
       </c>
       <c r="U12" t="n">
-        <v>5.324400000000001</v>
+        <v>5.324199999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.03109999999999991</v>
       </c>
       <c r="W12" t="n">
-        <v>7.000400000000001</v>
+        <v>7.0004</v>
       </c>
       <c r="X12" t="n">
         <v>-6.9693</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4928</v>
+        <v>5.0483</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4198</v>
+        <v>3.7736</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0731</v>
+        <v>1.2747</v>
       </c>
       <c r="G13" t="n">
         <v>4.5414</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8013</v>
+        <v>-0.2458</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2443</v>
+        <v>0.4459</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5577</v>
+        <v>2.6078</v>
       </c>
       <c r="E14" t="n">
-        <v>0.773</v>
+        <v>0.6551</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7847</v>
+        <v>1.9527</v>
       </c>
       <c r="G14" t="n">
         <v>0.9714</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1946</v>
+        <v>0.2447</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3791</v>
+        <v>0.5472</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6691</v>
+        <v>1.2424</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.3594</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0174</v>
+        <v>-0.117</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2279</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4946</v>
+        <v>0.0786</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3443</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8496</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.287</v>
+        <v>1.1961</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0806</v>
+        <v>-0.2599</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3676</v>
+        <v>1.456</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6696</v>
+        <v>0.5808</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1141</v>
+        <v>-3.2101</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5555</v>
+        <v>3.7909</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0525</v>
+        <v>1.4931</v>
       </c>
       <c r="K16" t="n">
-        <v>0.39</v>
+        <v>-2.1973</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6625</v>
+        <v>3.6904</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3829</v>
+        <v>-0.9122</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2759</v>
+        <v>-1.0127</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.107</v>
+        <v>0.1005</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0091</v>
+        <v>0.1513</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1142</v>
+        <v>-0.5933</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8949</v>
+        <v>0.7446</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0344</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0856</v>
+        <v>0.1865</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>-0.2497</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5808</v>
+        <v>0.1036</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.2101</v>
+        <v>-0.2711</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7909</v>
+        <v>0.3747</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4931</v>
+        <v>0.5795</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1973</v>
+        <v>0.1512</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6904</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9122</v>
+        <v>-0.4759</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0127</v>
+        <v>-0.4223</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1005</v>
+        <v>-0.0535</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0104</v>
+        <v>-0.1847</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4189</v>
+        <v>-0.393</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4086</v>
+        <v>0.2082</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0883</v>
+        <v>-0.4873</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6984</v>
+        <v>-0.5524</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6101</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4115</v>
+        <v>0.6696</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2413</v>
+        <v>0.1141</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8298</v>
+        <v>0.5555</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0296</v>
+        <v>1.0525</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3815</v>
+        <v>0.39</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3519</v>
+        <v>0.6625</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3819</v>
+        <v>-0.3829</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1401</v>
+        <v>-0.2759</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5221</v>
+        <v>-0.107</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4796</v>
+        <v>0.2348</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4086</v>
+        <v>-0.3576</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8881</v>
+        <v>0.5924</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8197</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6859</v>
+        <v>-0.8112</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1674</v>
+        <v>-2.8164</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5185</v>
+        <v>2.0052</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1036</v>
+        <v>0.4115</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2711</v>
+        <v>1.2413</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3747</v>
+        <v>-0.8298</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5795</v>
+        <v>0.0296</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1512</v>
+        <v>1.3815</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4282</v>
+        <v>-1.3519</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4759</v>
+        <v>0.3819</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4223</v>
+        <v>-0.1401</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0535</v>
+        <v>0.5221</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8074</v>
+        <v>0.7567</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7468</v>
+        <v>-0.5265</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0606</v>
+        <v>1.2832</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.8197</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5707</v>
+        <v>-1.9081</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2965</v>
+        <v>-2.7683</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7258</v>
+        <v>0.8602</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4521</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1133</v>
+        <v>-0.224</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1098</v>
+        <v>-0.5816</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6678</v>
+        <v>-2.6615</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3592</v>
+        <v>-2.1849</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3086</v>
+        <v>-0.4767</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4991</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4369</v>
+        <v>0.4433</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7512</v>
+        <v>-0.0745</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6858</v>
+        <v>0.5177</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1954</v>
+        <v>-5.2296</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1448</v>
+        <v>-5.3807</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0506</v>
+        <v>0.151</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9568</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0255</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1933</v>
+        <v>0.3949</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.223</v>
+        <v>-5.3239</v>
       </c>
       <c r="E23" t="n">
         <v>-4.6508</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5722</v>
+        <v>-0.673</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2898</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3818</v>
+        <v>-0.4826</v>
       </c>
       <c r="T23" t="n">
         <v>-0.7468</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3901</v>
+        <v>-6.3902</v>
       </c>
       <c r="E24" t="n">
         <v>-12.6388</v>
       </c>
       <c r="F24" t="n">
-        <v>6.248799999999999</v>
+        <v>6.248499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1474</v>
@@ -2329,10 +2329,10 @@
         <v>0.7468000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.3243</v>
+        <v>-5.3245</v>
       </c>
       <c r="U24" t="n">
-        <v>6.0714</v>
+        <v>6.071099999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.03109999999999968</v>
